--- a/data/raw/sales/Week 14/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 14/Audio_Array/other_channels.xlsx
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E5" s="25" t="n">
@@ -11054,13 +11054,15 @@
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="44">
-        <f>_xlfn.XLOOKUP(C25,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
-      </c>
-      <c r="B25" s="44">
-        <f>_xlfn.XLOOKUP(C25,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>FBA79982</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>AK-61 Pro</t>
+        </is>
       </c>
       <c r="C25" s="44" t="inlineStr">
         <is>
@@ -11158,7 +11160,7 @@
       </c>
       <c r="B28" s="44" t="inlineStr">
         <is>
-          <t>AH-60 RD</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="C28" s="44" t="inlineStr">
@@ -11811,13 +11813,15 @@
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="44">
-        <f>_xlfn.XLOOKUP(C48,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
-      </c>
-      <c r="B48" s="44">
-        <f>_xlfn.XLOOKUP(C48,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>FBA79980</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>AK-37-W</t>
+        </is>
       </c>
       <c r="C48" s="44" t="inlineStr">
         <is>
@@ -11882,7 +11886,7 @@
       </c>
       <c r="B50" s="44" t="inlineStr">
         <is>
-          <t>AH-60 BL</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="C50" s="44" t="inlineStr">
@@ -12139,13 +12143,15 @@
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="44">
-        <f>_xlfn.XLOOKUP(C58,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
-      </c>
-      <c r="B58" s="44">
-        <f>_xlfn.XLOOKUP(C58,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>FBA79981</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>AK-61 Neo</t>
+        </is>
       </c>
       <c r="C58" s="44" t="inlineStr">
         <is>
@@ -12302,13 +12308,15 @@
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="44">
-        <f>_xlfn.XLOOKUP(C63,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
-      </c>
-      <c r="B63" s="44">
-        <f>_xlfn.XLOOKUP(C63,[1]Sheet1!$C:$C,[1]Sheet1!$A:$A)</f>
-        <v/>
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>FBA79979</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>AK-37-B</t>
+        </is>
       </c>
       <c r="C63" s="44" t="inlineStr">
         <is>
@@ -12472,7 +12480,7 @@
       </c>
       <c r="B68" s="44" t="inlineStr">
         <is>
-          <t>AM-W22 Duplicate</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="C68" s="44" t="inlineStr">
@@ -13231,7 +13239,7 @@
       </c>
       <c r="B91" s="44" t="inlineStr">
         <is>
-          <t>AM-Mix8</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="C91" s="44" t="inlineStr">
